--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260228_201409.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260228_201409.xlsx
@@ -5478,7 +5478,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260228_201409.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260228_201409.xlsx
@@ -5478,7 +5478,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
